--- a/Docs/KNOWLEDGE_BASE/REGISTRY/OPEN_DECISION_REGISTRY.xlsx
+++ b/Docs/KNOWLEDGE_BASE/REGISTRY/OPEN_DECISION_REGISTRY.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" r:id="R31f79b7af6894f1c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据" sheetId="2" r:id="R00bc265e27274a70"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" r:id="Rae326d0976544cfc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据" sheetId="2" r:id="R49decabf809b4cfa"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -569,8 +569,7 @@
         <x:v>记录数</x:v>
       </x:c>
       <x:c r="B2" s="7" t="n">
-        <x:f>COUNTA(A4:A5)</x:f>
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
@@ -622,6 +621,23 @@
       </x:c>
       <x:c r="E5" t="str">
         <x:v>追加V72智能决策、Arena、模型和后续缺口记录；既有行保持不变。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>OPEN_DECISION_REGISTRY.xlsx</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:v>LUOYANG-184-T4-LIVING-WORLD-COMPLETION-MASTER-V1</x:v>
+      </x:c>
+      <x:c r="C6" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E6" t="str">
+        <x:v>追加洛阳T4 Phase 0—19正式状态、完成证据与Deferred边界；既有行保持不变。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -630,7 +646,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6f229b659e44427d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R535676723c7f4c5c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -677,8 +693,7 @@
         <x:v>记录数</x:v>
       </x:c>
       <x:c r="B2" s="7" t="n">
-        <x:f>COUNTA(A4:A35)</x:f>
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
@@ -1924,13 +1939,155 @@
       <x:c r="N35" s="56"/>
       <x:c r="O35" s="56"/>
     </x:row>
+    <x:row r="36">
+      <x:c r="A36" t="str">
+        <x:v>OPEN-LUOYANG-T4-001</x:v>
+      </x:c>
+      <x:c r="B36" t="str">
+        <x:v>LuoyangLivingWorld</x:v>
+      </x:c>
+      <x:c r="C36" t="str">
+        <x:v>东汉洛阳实物税率、免役减免及城门逐路重算何时进入正式深化？</x:v>
+      </x:c>
+      <x:c r="D36" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="E36" t="str">
+        <x:v>T4核心闭环已成立，但精确历史参数与逐Shipment动态路线不属于V1完成线</x:v>
+      </x:c>
+      <x:c r="F36" t="str">
+        <x:v>税制史料校准与路线性能证据</x:v>
+      </x:c>
+      <x:c r="G36" t="str">
+        <x:v>Future task owner</x:v>
+      </x:c>
+      <x:c r="H36" t="str">
+        <x:v>Does not block T4 V1</x:v>
+      </x:c>
+      <x:c r="I36" t="str">
+        <x:v>Docs/HISTORICAL_WORLD_REFERENCE/LUOYANG_184_T4_LIVING_WORLD_COMPLETION_MASTER_V1/15_POST_LUOYANG_T4_WORLD_EXPANSION_PLAN.md</x:v>
+      </x:c>
+      <x:c r="J36" t="str">
+        <x:v>Post-T4 planning</x:v>
+      </x:c>
+      <x:c r="K36" t="str">
+        <x:v>不得静默改写Frozen税制或地图合同</x:v>
+      </x:c>
+      <x:c r="L36"/>
+      <x:c r="M36"/>
+      <x:c r="N36" t="str">
+        <x:v>MEDIUM</x:v>
+      </x:c>
+      <x:c r="O36" t="str">
+        <x:v>Post-T4 review</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" t="str">
+        <x:v>open.map-presentation.final-3d-kit.v1</x:v>
+      </x:c>
+      <x:c r="B37" t="str">
+        <x:v>MapPresentation</x:v>
+      </x:c>
+      <x:c r="C37" t="str">
+        <x:v>Which final 3D Han modular art production method replaces procedural V1 markers?</x:v>
+      </x:c>
+      <x:c r="D37" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="E37" t="str">
+        <x:v>Golden Slice is playable but final 3D prefab art is deferred.</x:v>
+      </x:c>
+      <x:c r="F37" t="str">
+        <x:v>Art production benchmark and license audit</x:v>
+      </x:c>
+      <x:c r="G37" t="str"/>
+      <x:c r="H37" t="str">
+        <x:v>Full Luoyang presentation</x:v>
+      </x:c>
+      <x:c r="I37" t="str">
+        <x:v>Docs/TASK_LUOYANG_PLAYABLE_VERTICAL_SLICE_MAP_PRESENTATION_AND_CONSTRUCTION_ASSET_LIBRARY_V1.md</x:v>
+      </x:c>
+      <x:c r="J37" t="str"/>
+      <x:c r="K37" t="str"/>
+      <x:c r="L37" t="str"/>
+      <x:c r="M37" t="str"/>
+      <x:c r="N37" t="str"/>
+      <x:c r="O37" t="str"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" t="str">
+        <x:v>open.global-spatial.henan-terrain-detail-resolution.v1</x:v>
+      </x:c>
+      <x:c r="B38" t="str">
+        <x:v>GlobalSpatialFoundation</x:v>
+      </x:c>
+      <x:c r="C38" t="str">
+        <x:v>Which licensed source and production resolution will drive the first high-detail Henan Yin terrain?</x:v>
+      </x:c>
+      <x:c r="D38" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="E38" t="str">
+        <x:v>V1 freezes alignment, not final high-detail terrain content.</x:v>
+      </x:c>
+      <x:c r="F38" t="str">
+        <x:v>DEM source/license/accuracy/performance benchmark</x:v>
+      </x:c>
+      <x:c r="G38" t="str"/>
+      <x:c r="H38" t="str">
+        <x:v>HENAN-YIN-REGION-TERRAIN-AND-LUOYANG-BUILDABLE-MAP-V1</x:v>
+      </x:c>
+      <x:c r="I38" t="str">
+        <x:v>Docs/HISTORICAL_WORLD_REFERENCE/WORLD_GLOBAL_ORIGIN_CELL_GRID_AND_SPATIAL_CONTINUITY_V1/WORLD_GLOBAL_ORIGIN_CELL_GRID_AND_SPATIAL_CONTINUITY_V1_REPORT.md</x:v>
+      </x:c>
+      <x:c r="J38" t="str"/>
+      <x:c r="K38" t="str"/>
+      <x:c r="L38" t="str"/>
+      <x:c r="M38" t="str"/>
+      <x:c r="N38" t="str"/>
+      <x:c r="O38" t="str"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" t="str">
+        <x:v>open.global-spatial.region-production-boundaries.v1</x:v>
+      </x:c>
+      <x:c r="B39" t="str">
+        <x:v>GlobalSpatialFoundation</x:v>
+      </x:c>
+      <x:c r="C39" t="str">
+        <x:v>Which future chunk-aligned production Regions follow Henan Yin?</x:v>
+      </x:c>
+      <x:c r="D39" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="E39" t="str">
+        <x:v>Region is an optimization/art unit, not an administrative layer.</x:v>
+      </x:c>
+      <x:c r="F39" t="str">
+        <x:v>Terrain/streaming/art workload and gameplay corridor priorities</x:v>
+      </x:c>
+      <x:c r="G39" t="str"/>
+      <x:c r="H39" t="str">
+        <x:v>Does not block Henan Yin</x:v>
+      </x:c>
+      <x:c r="I39" t="str">
+        <x:v>Docs/HISTORICAL_WORLD_REFERENCE/WORLD_GLOBAL_ORIGIN_CELL_GRID_AND_SPATIAL_CONTINUITY_V1/GLOBAL_SPATIAL_FOUNDATION_CONTRACT_V1.md</x:v>
+      </x:c>
+      <x:c r="J39" t="str"/>
+      <x:c r="K39" t="str"/>
+      <x:c r="L39" t="str"/>
+      <x:c r="M39" t="str"/>
+      <x:c r="N39" t="str"/>
+      <x:c r="O39" t="str"/>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:L1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9749a5b589ee49b7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R38f414eab5f54633"/>
   </x:tableParts>
 </x:worksheet>
 </file>